--- a/output/StructureDefinition-t-cabs-observation-ahi.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-ahi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-ahi.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-ahi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-ahi.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-ahi.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5275" uniqueCount="739">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-ahi</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-ahi</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-beatmungsparameter</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-beatmungsparameter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -716,7 +716,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-procedure-beatmung)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-procedure-beatmung)
 </t>
   </si>
   <si>
@@ -878,7 +878,8 @@
     <t>Code defined by a terminology system</t>
   </si>
   <si>
-    <t>A reference to a code defined by a terminology system.</t>
+    <t>Total number of all apnoea and hypopnoea events occurring during a usage session divided by the hours of sleep
+* effective[x] only Period</t>
   </si>
   <si>
     <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
@@ -1062,7 +1063,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -1151,56 +1152,60 @@
 </t>
   </si>
   <si>
+    <t>dateTime
+PeriodTiminginstant</t>
+  </si>
+  <si>
+    <t>Clinically relevant time/time-period for observation</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+  </si>
+  <si>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+  </si>
+  <si>
+    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Numeric::Absolute-Time-Stamp</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectivePeriod</t>
+  </si>
+  <si>
+    <t>effectivePeriod</t>
+  </si>
+  <si>
     <t xml:space="preserve">Period
 </t>
   </si>
   <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
-  </si>
-  <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
-  </si>
-  <si>
-    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectiveDateTime</t>
-  </si>
-  <si>
-    <t>effectiveDateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Numeric::Absolute-Time-Stamp</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectivePeriod</t>
-  </si>
-  <si>
-    <t>effectivePeriod</t>
-  </si>
-  <si>
     <t>Observation.effective[x]:effectivePeriod.id</t>
   </si>
   <si>
@@ -1818,6 +1823,9 @@
     <t>Observation.bodySite.coding</t>
   </si>
   <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
     <t>Observation.bodySite.coding.id</t>
   </si>
   <si>
@@ -1909,7 +1917,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-devicemetric-numericmetric)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-devicemetric-numericmetric)
 </t>
   </si>
   <si>
@@ -7897,7 +7905,7 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>364</v>
@@ -7999,10 +8007,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8123,10 +8131,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8249,10 +8257,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8278,13 +8286,13 @@
         <v>375</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8334,7 +8342,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8343,16 +8351,16 @@
         <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>84</v>
@@ -8361,10 +8369,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8375,10 +8383,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8404,20 +8412,20 @@
         <v>375</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="R46" t="s" s="2">
         <v>84</v>
@@ -8462,7 +8470,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8471,16 +8479,16 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -8489,10 +8497,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8503,13 +8511,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>362</v>
@@ -8610,7 +8618,7 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>369</v>
@@ -8633,10 +8641,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8662,13 +8670,13 @@
         <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8718,7 +8726,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8745,13 +8753,13 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8759,10 +8767,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8785,17 +8793,17 @@
         <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8844,7 +8852,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8865,19 +8873,19 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -8885,10 +8893,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8911,19 +8919,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8970,7 +8978,7 @@
         <v>368</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8979,7 +8987,7 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
@@ -8994,30 +9002,30 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>84</v>
@@ -9039,19 +9047,19 @@
         <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -9100,7 +9108,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9109,7 +9117,7 @@
         <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>107</v>
@@ -9124,27 +9132,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9265,10 +9273,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9391,10 +9399,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9417,19 +9425,19 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9478,7 +9486,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9493,10 +9501,10 @@
         <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>84</v>
@@ -9505,10 +9513,10 @@
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9519,10 +9527,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9548,20 +9556,20 @@
         <v>172</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R55" t="s" s="2">
         <v>84</v>
@@ -9585,10 +9593,10 @@
         <v>236</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9606,7 +9614,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9633,10 +9641,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9647,10 +9655,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9676,14 +9684,14 @@
         <v>109</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9732,7 +9740,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9759,10 +9767,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9773,10 +9781,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9802,21 +9810,21 @@
         <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>84</v>
@@ -9858,7 +9866,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9867,7 +9875,7 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
@@ -9885,10 +9893,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9899,10 +9907,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9928,16 +9936,16 @@
         <v>172</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9947,7 +9955,7 @@
         <v>84</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>84</v>
@@ -9986,7 +9994,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10001,7 +10009,7 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>84</v>
@@ -10013,10 +10021,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -10027,13 +10035,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>84</v>
@@ -10055,19 +10063,19 @@
         <v>96</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10116,7 +10124,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10125,7 +10133,7 @@
         <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
@@ -10140,27 +10148,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10281,10 +10289,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10407,10 +10415,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10433,13 +10441,13 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10490,7 +10498,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10520,7 +10528,7 @@
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10531,10 +10539,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10655,10 +10663,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10781,10 +10789,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10807,19 +10815,19 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10868,7 +10876,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10895,10 +10903,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10909,10 +10917,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10938,20 +10946,20 @@
         <v>172</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R66" t="s" s="2">
         <v>84</v>
@@ -10975,10 +10983,10 @@
         <v>236</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -10996,7 +11004,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11023,10 +11031,10 @@
         <v>84</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11037,10 +11045,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11066,14 +11074,14 @@
         <v>109</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11122,7 +11130,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11149,10 +11157,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11163,10 +11171,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11192,21 +11200,21 @@
         <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>84</v>
@@ -11248,7 +11256,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11257,7 +11265,7 @@
         <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>107</v>
@@ -11275,10 +11283,10 @@
         <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11289,10 +11297,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11318,16 +11326,16 @@
         <v>172</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11376,7 +11384,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11403,10 +11411,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11417,10 +11425,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11443,13 +11451,13 @@
         <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11500,7 +11508,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11530,7 +11538,7 @@
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11541,10 +11549,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11665,10 +11673,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11791,10 +11799,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11817,19 +11825,19 @@
         <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11878,7 +11886,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11905,10 +11913,10 @@
         <v>84</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11919,10 +11927,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11948,20 +11956,20 @@
         <v>172</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R74" t="s" s="2">
         <v>84</v>
@@ -11985,10 +11993,10 @@
         <v>236</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12006,7 +12014,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12033,10 +12041,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12047,10 +12055,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12076,14 +12084,14 @@
         <v>109</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -12132,7 +12140,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12159,10 +12167,10 @@
         <v>84</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12173,10 +12181,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12202,21 +12210,21 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>84</v>
@@ -12258,7 +12266,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12267,7 +12275,7 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
@@ -12285,10 +12293,10 @@
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12299,10 +12307,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12328,16 +12336,16 @@
         <v>172</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12386,7 +12394,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12413,10 +12421,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12427,10 +12435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12456,16 +12464,16 @@
         <v>245</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12493,10 +12501,10 @@
         <v>153</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12514,7 +12522,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12523,7 +12531,7 @@
         <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>107</v>
@@ -12544,7 +12552,7 @@
         <v>195</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12555,14 +12563,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12584,16 +12592,16 @@
         <v>245</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12622,7 +12630,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12640,7 +12648,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12658,33 +12666,33 @@
         <v>157</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12707,19 +12715,19 @@
         <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12768,7 +12776,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12795,10 +12803,10 @@
         <v>84</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12809,10 +12817,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12838,13 +12846,13 @@
         <v>245</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12873,10 +12881,10 @@
         <v>162</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -12894,7 +12902,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12918,27 +12926,27 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13059,10 +13067,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13185,10 +13193,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13217,7 +13225,7 @@
         <v>274</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>275</v>
+        <v>581</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>276</v>
@@ -13313,10 +13321,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13437,10 +13445,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13563,10 +13571,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13668,7 +13676,7 @@
         <v>84</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>84</v>
@@ -13691,10 +13699,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13794,7 +13802,7 @@
         <v>84</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>84</v>
@@ -13817,10 +13825,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13920,7 +13928,7 @@
         <v>84</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>84</v>
@@ -13943,10 +13951,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14069,10 +14077,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14197,10 +14205,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14325,10 +14333,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14354,16 +14362,16 @@
         <v>245</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14391,10 +14399,10 @@
         <v>162</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14412,7 +14420,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14439,10 +14447,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14453,10 +14461,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14479,16 +14487,16 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14538,7 +14546,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14562,27 +14570,27 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14605,16 +14613,16 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14664,7 +14672,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14688,27 +14696,27 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14731,19 +14739,19 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -14792,7 +14800,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14804,7 +14812,7 @@
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14819,10 +14827,10 @@
         <v>84</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
@@ -14833,10 +14841,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14957,10 +14965,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15083,14 +15091,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -15112,10 +15120,10 @@
         <v>116</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>119</v>
@@ -15170,7 +15178,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15211,10 +15219,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15237,13 +15245,13 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -15294,7 +15302,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15303,16 +15311,16 @@
         <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>84</v>
@@ -15321,10 +15329,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15335,10 +15343,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15459,10 +15467,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15585,10 +15593,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15611,19 +15619,19 @@
         <v>96</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -15672,7 +15680,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15699,10 +15707,10 @@
         <v>84</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -15713,10 +15721,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15742,20 +15750,20 @@
         <v>172</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q104" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R104" t="s" s="2">
         <v>84</v>
@@ -15779,10 +15787,10 @@
         <v>236</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>84</v>
@@ -15800,7 +15808,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15827,10 +15835,10 @@
         <v>84</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -15841,10 +15849,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15870,14 +15878,14 @@
         <v>109</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
@@ -15926,7 +15934,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -15953,10 +15961,10 @@
         <v>84</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
@@ -15967,10 +15975,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15996,14 +16004,14 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>84</v>
@@ -16013,7 +16021,7 @@
         <v>84</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>84</v>
@@ -16052,7 +16060,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16061,7 +16069,7 @@
         <v>95</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>107</v>
@@ -16079,10 +16087,10 @@
         <v>84</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
@@ -16093,10 +16101,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16122,16 +16130,16 @@
         <v>172</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
@@ -16180,7 +16188,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16207,10 +16215,10 @@
         <v>84</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
@@ -16221,10 +16229,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16247,13 +16255,13 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16304,7 +16312,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16313,16 +16321,16 @@
         <v>95</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>84</v>
@@ -16331,10 +16339,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16345,10 +16353,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16469,10 +16477,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16595,10 +16603,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16621,19 +16629,19 @@
         <v>96</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -16682,7 +16690,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16709,10 +16717,10 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16723,10 +16731,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16752,20 +16760,20 @@
         <v>172</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q112" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R112" t="s" s="2">
         <v>84</v>
@@ -16789,10 +16797,10 @@
         <v>236</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -16810,7 +16818,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -16837,10 +16845,10 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -16851,10 +16859,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16880,14 +16888,14 @@
         <v>109</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -16936,7 +16944,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -16963,10 +16971,10 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -16977,10 +16985,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17006,14 +17014,14 @@
         <v>137</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
@@ -17023,7 +17031,7 @@
         <v>84</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>84</v>
@@ -17062,7 +17070,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17071,7 +17079,7 @@
         <v>95</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>107</v>
@@ -17089,10 +17097,10 @@
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17103,10 +17111,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17132,16 +17140,16 @@
         <v>172</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17190,7 +17198,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17217,10 +17225,10 @@
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17231,10 +17239,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17260,16 +17268,16 @@
         <v>245</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17279,7 +17287,7 @@
         <v>84</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>84</v>
@@ -17297,10 +17305,10 @@
         <v>176</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17318,7 +17326,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17342,13 +17350,13 @@
         <v>84</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17359,10 +17367,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17388,16 +17396,16 @@
         <v>245</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17425,10 +17433,10 @@
         <v>162</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
@@ -17446,7 +17454,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17470,13 +17478,13 @@
         <v>84</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -17487,10 +17495,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17513,17 +17521,17 @@
         <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17572,7 +17580,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17602,7 +17610,7 @@
         <v>84</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
@@ -17613,10 +17621,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17642,10 +17650,10 @@
         <v>109</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17696,7 +17704,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17723,10 +17731,10 @@
         <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
@@ -17737,10 +17745,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17763,16 +17771,16 @@
         <v>96</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17822,7 +17830,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -17849,10 +17857,10 @@
         <v>84</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AQ120" t="s" s="2">
         <v>84</v>
@@ -17863,10 +17871,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17889,16 +17897,16 @@
         <v>96</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17948,7 +17956,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -17975,10 +17983,10 @@
         <v>84</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -17989,10 +17997,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18015,19 +18023,19 @@
         <v>96</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18076,7 +18084,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18103,10 +18111,10 @@
         <v>84</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18117,10 +18125,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18241,10 +18249,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18367,14 +18375,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -18396,10 +18404,10 @@
         <v>116</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>119</v>
@@ -18454,7 +18462,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18495,10 +18503,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18524,13 +18532,13 @@
         <v>245</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>263</v>
@@ -18561,10 +18569,10 @@
         <v>162</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18582,7 +18590,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>95</v>
@@ -18606,7 +18614,7 @@
         <v>84</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>267</v>
@@ -18623,10 +18631,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18649,19 +18657,19 @@
         <v>96</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
@@ -18710,7 +18718,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18734,27 +18742,27 @@
         <v>84</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18780,16 +18788,16 @@
         <v>245</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -18817,10 +18825,10 @@
         <v>153</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>84</v>
@@ -18838,7 +18846,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -18847,7 +18855,7 @@
         <v>95</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>107</v>
@@ -18868,7 +18876,7 @@
         <v>195</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
@@ -18879,14 +18887,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -18908,16 +18916,16 @@
         <v>245</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -18945,28 +18953,28 @@
         <v>153</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="Z129" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -18990,27 +18998,27 @@
         <v>84</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR129" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19036,16 +19044,16 @@
         <v>85</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19094,7 +19102,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19121,10 +19129,10 @@
         <v>84</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
